--- a/data/report.xlsx
+++ b/data/report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30509"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bank Muscat\AD Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="390" documentId="13_ncr:1_{4A272BF1-49BC-4E00-83C3-F2030B573C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95D7CB3C-75A2-40C6-B5DD-5CECF53324A3}"/>
+  <xr:revisionPtr revIDLastSave="395" documentId="13_ncr:1_{4A272BF1-49BC-4E00-83C3-F2030B573C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89024CE3-EC2F-4ED2-82FB-9464D4955AF4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="278">
   <si>
     <t>Client / entity</t>
   </si>
@@ -909,6 +909,12 @@
   </si>
   <si>
     <t>LLMApp /getResponse JSON consumed by the AD SOE portal; DataApp Postgres tables per measure + analysis cache; IOApp markdown of uploaded documents in MinIO; MinIOApp document list/get/delete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project Test </t>
+  </si>
+  <si>
+    <t>Anomaly Deyection in Bank</t>
   </si>
 </sst>
 </file>
@@ -1050,7 +1056,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1138,12 +1144,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1217,9 +1247,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1244,9 +1271,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1264,6 +1288,36 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1589,7 +1643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AG12"/>
+  <dimension ref="A1:AG13"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="23" customWidth="1"/>
@@ -1714,21 +1768,21 @@
       <c r="AB1" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="31" t="s">
+      <c r="AC1" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="27" t="s">
+      <c r="AD1" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="27" t="s">
+      <c r="AE1" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="27" t="s">
+      <c r="AF1" s="26" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:33" s="14" customFormat="1" ht="166.5">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="33" t="s">
         <v>32</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1810,17 +1864,17 @@
       <c r="AB2" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC2" s="32" t="s">
+      <c r="AC2" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="AD2" s="28"/>
-      <c r="AE2" s="28"/>
-      <c r="AF2" s="28" t="s">
+      <c r="AD2" s="27"/>
+      <c r="AE2" s="27"/>
+      <c r="AF2" s="27" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:33" s="14" customFormat="1" ht="130.5">
-      <c r="A3" s="36"/>
+      <c r="A3" s="34"/>
       <c r="B3" s="1" t="s">
         <v>61</v>
       </c>
@@ -1900,12 +1954,12 @@
       <c r="AB3" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AC3" s="32" t="s">
+      <c r="AC3" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="AD3" s="28"/>
-      <c r="AE3" s="28"/>
-      <c r="AF3" s="28" t="s">
+      <c r="AD3" s="27"/>
+      <c r="AE3" s="27"/>
+      <c r="AF3" s="27" t="s">
         <v>60</v>
       </c>
       <c r="AG3" s="14" t="s">
@@ -1913,7 +1967,7 @@
       </c>
     </row>
     <row r="4" spans="1:33" s="17" customFormat="1" ht="63.6" customHeight="1">
-      <c r="A4" s="37"/>
+      <c r="A4" s="35"/>
       <c r="B4" s="1" t="s">
         <v>72</v>
       </c>
@@ -1985,12 +2039,12 @@
       <c r="AB4" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="AC4" s="33" t="s">
+      <c r="AC4" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="AD4" s="29"/>
-      <c r="AE4" s="29"/>
-      <c r="AF4" s="28" t="s">
+      <c r="AD4" s="28"/>
+      <c r="AE4" s="28"/>
+      <c r="AF4" s="27" t="s">
         <v>60</v>
       </c>
       <c r="AG4" s="14" t="s">
@@ -1998,7 +2052,7 @@
       </c>
     </row>
     <row r="5" spans="1:33" s="17" customFormat="1" ht="84">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="36" t="s">
         <v>89</v>
       </c>
       <c r="B5" s="15" t="s">
@@ -2082,15 +2136,15 @@
       <c r="AB5" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="AC5" s="33" t="s">
+      <c r="AC5" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="AD5" s="29"/>
-      <c r="AE5" s="29"/>
-      <c r="AF5" s="29"/>
+      <c r="AD5" s="28"/>
+      <c r="AE5" s="28"/>
+      <c r="AF5" s="28"/>
     </row>
     <row r="6" spans="1:33" s="17" customFormat="1" ht="84">
-      <c r="A6" s="39"/>
+      <c r="A6" s="37"/>
       <c r="B6" s="15" t="s">
         <v>117</v>
       </c>
@@ -2172,15 +2226,15 @@
       <c r="AB6" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="AC6" s="33" t="s">
+      <c r="AC6" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="AD6" s="29"/>
-      <c r="AE6" s="29"/>
-      <c r="AF6" s="29"/>
+      <c r="AD6" s="28"/>
+      <c r="AE6" s="28"/>
+      <c r="AF6" s="28"/>
     </row>
     <row r="7" spans="1:33" s="17" customFormat="1" ht="72">
-      <c r="A7" s="40"/>
+      <c r="A7" s="38"/>
       <c r="B7" s="15" t="s">
         <v>142</v>
       </c>
@@ -2262,15 +2316,15 @@
       <c r="AB7" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="AC7" s="33" t="s">
+      <c r="AC7" s="32" t="s">
         <v>166</v>
       </c>
-      <c r="AD7" s="29"/>
-      <c r="AE7" s="29"/>
-      <c r="AF7" s="29"/>
+      <c r="AD7" s="28"/>
+      <c r="AE7" s="28"/>
+      <c r="AF7" s="28"/>
     </row>
     <row r="8" spans="1:33" ht="130.5" customHeight="1">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="36" t="s">
         <v>167</v>
       </c>
       <c r="B8" s="15" t="s">
@@ -2354,18 +2408,18 @@
       <c r="AB8" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="AC8" s="33" t="s">
+      <c r="AC8" s="32" t="s">
         <v>194</v>
       </c>
-      <c r="AD8" s="29"/>
-      <c r="AE8" s="29"/>
-      <c r="AF8" s="28" t="s">
+      <c r="AD8" s="28"/>
+      <c r="AE8" s="28"/>
+      <c r="AF8" s="27" t="s">
         <v>195</v>
       </c>
       <c r="AG8" s="17"/>
     </row>
     <row r="9" spans="1:33" s="23" customFormat="1" ht="122.25" customHeight="1">
-      <c r="A9" s="40"/>
+      <c r="A9" s="38"/>
       <c r="B9" s="15" t="s">
         <v>196</v>
       </c>
@@ -2375,7 +2429,7 @@
       <c r="D9" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="E9" s="25" t="s">
         <v>198</v>
       </c>
       <c r="F9" s="16" t="s">
@@ -2433,12 +2487,12 @@
         <v>214</v>
       </c>
       <c r="AB9" s="16"/>
-      <c r="AC9" s="33" t="s">
+      <c r="AC9" s="32" t="s">
         <v>215</v>
       </c>
-      <c r="AD9" s="30"/>
-      <c r="AE9" s="30"/>
-      <c r="AF9" s="28" t="s">
+      <c r="AD9" s="29"/>
+      <c r="AE9" s="29"/>
+      <c r="AF9" s="27" t="s">
         <v>216</v>
       </c>
     </row>
@@ -2527,14 +2581,14 @@
       <c r="AB10" s="15" t="s">
         <v>224</v>
       </c>
-      <c r="AC10" s="33" t="s">
+      <c r="AC10" s="32" t="s">
         <v>224</v>
       </c>
-      <c r="AD10" s="29"/>
-      <c r="AE10" s="29" t="s">
+      <c r="AD10" s="28"/>
+      <c r="AE10" s="28" t="s">
         <v>232</v>
       </c>
-      <c r="AF10" s="29" t="s">
+      <c r="AF10" s="28" t="s">
         <v>233</v>
       </c>
     </row>
@@ -2623,105 +2677,147 @@
       <c r="AB11" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="AC11" s="33"/>
-      <c r="AD11" s="29"/>
-      <c r="AE11" s="29"/>
-      <c r="AF11" s="29"/>
+      <c r="AC11" s="32"/>
+      <c r="AD11" s="28"/>
+      <c r="AE11" s="28"/>
+      <c r="AF11" s="28"/>
       <c r="AG11" s="17"/>
     </row>
     <row r="12" spans="1:33" s="17" customFormat="1" ht="195" customHeight="1">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="41" t="s">
         <v>261</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="42" t="s">
         <v>262</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="42" t="s">
         <v>263</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="42" t="s">
         <v>264</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="43" t="s">
         <v>265</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="42" t="s">
         <v>266</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="42" t="s">
         <v>267</v>
       </c>
-      <c r="H12" s="15" t="s">
+      <c r="H12" s="42" t="s">
         <v>268</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="I12" s="42" t="s">
         <v>224</v>
       </c>
-      <c r="J12" s="18" t="s">
+      <c r="J12" s="44" t="s">
         <v>224</v>
       </c>
-      <c r="K12" s="16" t="s">
+      <c r="K12" s="45" t="s">
         <v>224</v>
       </c>
-      <c r="L12" s="16" t="s">
+      <c r="L12" s="45" t="s">
         <v>224</v>
       </c>
-      <c r="M12" s="16" t="s">
+      <c r="M12" s="45" t="s">
         <v>224</v>
       </c>
-      <c r="N12" s="16" t="s">
+      <c r="N12" s="45" t="s">
         <v>269</v>
       </c>
-      <c r="O12" s="16" t="s">
+      <c r="O12" s="45" t="s">
         <v>270</v>
       </c>
-      <c r="P12" s="15" t="s">
+      <c r="P12" s="42" t="s">
         <v>271</v>
       </c>
-      <c r="Q12" s="16" t="s">
+      <c r="Q12" s="45" t="s">
         <v>224</v>
       </c>
-      <c r="R12" s="16" t="s">
+      <c r="R12" s="45" t="s">
         <v>224</v>
       </c>
-      <c r="S12" s="16" t="s">
+      <c r="S12" s="45" t="s">
         <v>224</v>
       </c>
-      <c r="T12" s="15" t="s">
+      <c r="T12" s="42" t="s">
         <v>272</v>
       </c>
-      <c r="U12" s="16" t="s">
+      <c r="U12" s="45" t="s">
         <v>224</v>
       </c>
-      <c r="V12" s="16" t="s">
+      <c r="V12" s="45" t="s">
         <v>224</v>
       </c>
-      <c r="W12" s="16" t="s">
+      <c r="W12" s="45" t="s">
         <v>224</v>
       </c>
-      <c r="X12" s="16" t="s">
+      <c r="X12" s="45" t="s">
         <v>224</v>
       </c>
-      <c r="Y12" s="15" t="s">
+      <c r="Y12" s="42" t="s">
         <v>273</v>
       </c>
-      <c r="Z12" s="15" t="s">
+      <c r="Z12" s="42" t="s">
         <v>274</v>
       </c>
-      <c r="AA12" s="15" t="s">
+      <c r="AA12" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="AB12" s="16" t="s">
+      <c r="AB12" s="45" t="s">
         <v>224</v>
       </c>
-      <c r="AC12" s="34" t="s">
+      <c r="AC12" s="46" t="s">
         <v>224</v>
       </c>
-      <c r="AD12" s="29"/>
-      <c r="AE12" s="29"/>
-      <c r="AF12" s="28" t="s">
+      <c r="AD12" s="47"/>
+      <c r="AE12" s="47"/>
+      <c r="AF12" s="48" t="s">
         <v>216</v>
       </c>
+    </row>
+    <row r="13" spans="1:33" ht="24">
+      <c r="A13" s="29" t="s">
+        <v>276</v>
+      </c>
+      <c r="B13" s="39" t="s">
+        <v>277</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="39"/>
+      <c r="L13" s="39"/>
+      <c r="M13" s="39"/>
+      <c r="N13" s="40"/>
+      <c r="O13" s="39"/>
+      <c r="P13" s="39"/>
+      <c r="Q13" s="39"/>
+      <c r="R13" s="39"/>
+      <c r="S13" s="39"/>
+      <c r="T13" s="39"/>
+      <c r="U13" s="39"/>
+      <c r="V13" s="39"/>
+      <c r="W13" s="39"/>
+      <c r="X13" s="39" t="s">
+        <v>224</v>
+      </c>
+      <c r="Y13" s="39"/>
+      <c r="Z13" s="39"/>
+      <c r="AA13" s="39"/>
+      <c r="AB13" s="39"/>
+      <c r="AC13" s="39"/>
+      <c r="AD13" s="39"/>
+      <c r="AE13" s="39"/>
+      <c r="AF13" s="39"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AC2" xr:uid="{00000000-0009-0000-0000-000001000000}"/>

--- a/data/report.xlsx
+++ b/data/report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bank Muscat\AD Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="395" documentId="13_ncr:1_{4A272BF1-49BC-4E00-83C3-F2030B573C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89024CE3-EC2F-4ED2-82FB-9464D4955AF4}"/>
+  <xr:revisionPtr revIDLastSave="402" documentId="13_ncr:1_{4A272BF1-49BC-4E00-83C3-F2030B573C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B06732D-B0A2-4A73-B4F7-0F942316771B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="279">
   <si>
     <t>Client / entity</t>
   </si>
@@ -911,10 +911,13 @@
     <t>LLMApp /getResponse JSON consumed by the AD SOE portal; DataApp Postgres tables per measure + analysis cache; IOApp markdown of uploaded documents in MinIO; MinIOApp document list/get/delete</t>
   </si>
   <si>
-    <t xml:space="preserve">Project Test </t>
+    <t>Project Test 123</t>
   </si>
   <si>
     <t>Anomaly Deyection in Bank</t>
+  </si>
+  <si>
+    <t>Project Test 456</t>
   </si>
 </sst>
 </file>
@@ -1643,7 +1646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AG13"/>
+  <dimension ref="A1:AG14"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="23" customWidth="1"/>
@@ -2819,6 +2822,48 @@
       <c r="AE13" s="39"/>
       <c r="AF13" s="39"/>
     </row>
+    <row r="14" spans="1:33" ht="24">
+      <c r="A14" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="B14" s="39" t="s">
+        <v>277</v>
+      </c>
+      <c r="C14" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="39"/>
+      <c r="M14" s="39"/>
+      <c r="N14" s="40"/>
+      <c r="O14" s="39"/>
+      <c r="P14" s="39"/>
+      <c r="Q14" s="39"/>
+      <c r="R14" s="39"/>
+      <c r="S14" s="39"/>
+      <c r="T14" s="39"/>
+      <c r="U14" s="39"/>
+      <c r="V14" s="39"/>
+      <c r="W14" s="39"/>
+      <c r="X14" s="39" t="s">
+        <v>224</v>
+      </c>
+      <c r="Y14" s="39"/>
+      <c r="Z14" s="39"/>
+      <c r="AA14" s="39"/>
+      <c r="AB14" s="39"/>
+      <c r="AC14" s="39"/>
+      <c r="AD14" s="39"/>
+      <c r="AE14" s="39"/>
+      <c r="AF14" s="39"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AC2" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="3">
@@ -2827,7 +2872,7 @@
     <mergeCell ref="A8:A9"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="P2:P3 M3 W2 V3 M2:N2 I2:K3 M12:N12 U12:X12 N13:N203 AB12:AC12 N4:N11 Q4:Q203 R12:S12 W4:W11 W13:W203 J4:L203" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="P2:P3 M3 W2 V3 M2:N2 I2:K3 M12:N12 U12:X12 AB12:AC12 N4:N11 R12:S12 W4:W11 J4:L201 Q4:Q201 N13:N201 W13:W201" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Yes,No,Partial,N/A,Not recorded"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/data/report.xlsx
+++ b/data/report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bank Muscat\AD Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="402" documentId="13_ncr:1_{4A272BF1-49BC-4E00-83C3-F2030B573C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B06732D-B0A2-4A73-B4F7-0F942316771B}"/>
+  <xr:revisionPtr revIDLastSave="417" documentId="13_ncr:1_{4A272BF1-49BC-4E00-83C3-F2030B573C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0264B50-D87E-450A-8522-77D1B34FEEA7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="280">
   <si>
     <t>Client / entity</t>
   </si>
@@ -918,6 +918,9 @@
   </si>
   <si>
     <t>Project Test 456</t>
+  </si>
+  <si>
+    <t>Project Test 789100</t>
   </si>
 </sst>
 </file>
@@ -1176,7 +1179,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1274,6 +1277,30 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1291,36 +1318,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1646,11 +1643,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AG14"/>
+  <dimension ref="A1:AG15"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="23" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" style="22" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" style="22" customWidth="1"/>
     <col min="3" max="3" width="13.7109375" style="22" customWidth="1"/>
     <col min="4" max="4" width="24.140625" style="22" customWidth="1"/>
     <col min="5" max="5" width="19" style="22" customWidth="1"/>
@@ -1785,7 +1782,7 @@
       </c>
     </row>
     <row r="2" spans="1:33" s="14" customFormat="1" ht="166.5">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="41" t="s">
         <v>32</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1877,7 +1874,7 @@
       </c>
     </row>
     <row r="3" spans="1:33" s="14" customFormat="1" ht="130.5">
-      <c r="A3" s="34"/>
+      <c r="A3" s="42"/>
       <c r="B3" s="1" t="s">
         <v>61</v>
       </c>
@@ -1970,7 +1967,7 @@
       </c>
     </row>
     <row r="4" spans="1:33" s="17" customFormat="1" ht="63.6" customHeight="1">
-      <c r="A4" s="35"/>
+      <c r="A4" s="43"/>
       <c r="B4" s="1" t="s">
         <v>72</v>
       </c>
@@ -2055,7 +2052,7 @@
       </c>
     </row>
     <row r="5" spans="1:33" s="17" customFormat="1" ht="84">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="44" t="s">
         <v>89</v>
       </c>
       <c r="B5" s="15" t="s">
@@ -2147,7 +2144,7 @@
       <c r="AF5" s="28"/>
     </row>
     <row r="6" spans="1:33" s="17" customFormat="1" ht="84">
-      <c r="A6" s="37"/>
+      <c r="A6" s="45"/>
       <c r="B6" s="15" t="s">
         <v>117</v>
       </c>
@@ -2237,7 +2234,7 @@
       <c r="AF6" s="28"/>
     </row>
     <row r="7" spans="1:33" s="17" customFormat="1" ht="72">
-      <c r="A7" s="38"/>
+      <c r="A7" s="46"/>
       <c r="B7" s="15" t="s">
         <v>142</v>
       </c>
@@ -2327,7 +2324,7 @@
       <c r="AF7" s="28"/>
     </row>
     <row r="8" spans="1:33" ht="130.5" customHeight="1">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="44" t="s">
         <v>167</v>
       </c>
       <c r="B8" s="15" t="s">
@@ -2422,7 +2419,7 @@
       <c r="AG8" s="17"/>
     </row>
     <row r="9" spans="1:33" s="23" customFormat="1" ht="122.25" customHeight="1">
-      <c r="A9" s="38"/>
+      <c r="A9" s="46"/>
       <c r="B9" s="15" t="s">
         <v>196</v>
       </c>
@@ -2687,182 +2684,224 @@
       <c r="AG11" s="17"/>
     </row>
     <row r="12" spans="1:33" s="17" customFormat="1" ht="195" customHeight="1">
-      <c r="A12" s="41" t="s">
+      <c r="A12" s="33" t="s">
         <v>261</v>
       </c>
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="34" t="s">
         <v>262</v>
       </c>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="34" t="s">
         <v>263</v>
       </c>
-      <c r="D12" s="42" t="s">
+      <c r="D12" s="34" t="s">
         <v>264</v>
       </c>
-      <c r="E12" s="43" t="s">
+      <c r="E12" s="35" t="s">
         <v>265</v>
       </c>
-      <c r="F12" s="42" t="s">
+      <c r="F12" s="34" t="s">
         <v>266</v>
       </c>
-      <c r="G12" s="42" t="s">
+      <c r="G12" s="34" t="s">
         <v>267</v>
       </c>
-      <c r="H12" s="42" t="s">
+      <c r="H12" s="34" t="s">
         <v>268</v>
       </c>
-      <c r="I12" s="42" t="s">
-        <v>224</v>
-      </c>
-      <c r="J12" s="44" t="s">
-        <v>224</v>
-      </c>
-      <c r="K12" s="45" t="s">
-        <v>224</v>
-      </c>
-      <c r="L12" s="45" t="s">
-        <v>224</v>
-      </c>
-      <c r="M12" s="45" t="s">
-        <v>224</v>
-      </c>
-      <c r="N12" s="45" t="s">
+      <c r="I12" s="34" t="s">
+        <v>224</v>
+      </c>
+      <c r="J12" s="36" t="s">
+        <v>224</v>
+      </c>
+      <c r="K12" s="37" t="s">
+        <v>224</v>
+      </c>
+      <c r="L12" s="37" t="s">
+        <v>224</v>
+      </c>
+      <c r="M12" s="37" t="s">
+        <v>224</v>
+      </c>
+      <c r="N12" s="37" t="s">
         <v>269</v>
       </c>
-      <c r="O12" s="45" t="s">
+      <c r="O12" s="37" t="s">
         <v>270</v>
       </c>
-      <c r="P12" s="42" t="s">
+      <c r="P12" s="34" t="s">
         <v>271</v>
       </c>
-      <c r="Q12" s="45" t="s">
-        <v>224</v>
-      </c>
-      <c r="R12" s="45" t="s">
-        <v>224</v>
-      </c>
-      <c r="S12" s="45" t="s">
-        <v>224</v>
-      </c>
-      <c r="T12" s="42" t="s">
+      <c r="Q12" s="37" t="s">
+        <v>224</v>
+      </c>
+      <c r="R12" s="37" t="s">
+        <v>224</v>
+      </c>
+      <c r="S12" s="37" t="s">
+        <v>224</v>
+      </c>
+      <c r="T12" s="34" t="s">
         <v>272</v>
       </c>
-      <c r="U12" s="45" t="s">
-        <v>224</v>
-      </c>
-      <c r="V12" s="45" t="s">
-        <v>224</v>
-      </c>
-      <c r="W12" s="45" t="s">
-        <v>224</v>
-      </c>
-      <c r="X12" s="45" t="s">
-        <v>224</v>
-      </c>
-      <c r="Y12" s="42" t="s">
+      <c r="U12" s="37" t="s">
+        <v>224</v>
+      </c>
+      <c r="V12" s="37" t="s">
+        <v>224</v>
+      </c>
+      <c r="W12" s="37" t="s">
+        <v>224</v>
+      </c>
+      <c r="X12" s="37" t="s">
+        <v>224</v>
+      </c>
+      <c r="Y12" s="34" t="s">
         <v>273</v>
       </c>
-      <c r="Z12" s="42" t="s">
+      <c r="Z12" s="34" t="s">
         <v>274</v>
       </c>
-      <c r="AA12" s="42" t="s">
+      <c r="AA12" s="34" t="s">
         <v>275</v>
       </c>
-      <c r="AB12" s="45" t="s">
-        <v>224</v>
-      </c>
-      <c r="AC12" s="46" t="s">
-        <v>224</v>
-      </c>
-      <c r="AD12" s="47"/>
-      <c r="AE12" s="47"/>
-      <c r="AF12" s="48" t="s">
+      <c r="AB12" s="37" t="s">
+        <v>224</v>
+      </c>
+      <c r="AC12" s="38" t="s">
+        <v>224</v>
+      </c>
+      <c r="AD12" s="39"/>
+      <c r="AE12" s="39"/>
+      <c r="AF12" s="40" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="13" spans="1:33" ht="24">
+    <row r="13" spans="1:33" s="23" customFormat="1" ht="21.75" customHeight="1">
       <c r="A13" s="29" t="s">
         <v>276</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="29" t="s">
         <v>277</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="40"/>
-      <c r="K13" s="39"/>
-      <c r="L13" s="39"/>
-      <c r="M13" s="39"/>
-      <c r="N13" s="40"/>
-      <c r="O13" s="39"/>
-      <c r="P13" s="39"/>
-      <c r="Q13" s="39"/>
-      <c r="R13" s="39"/>
-      <c r="S13" s="39"/>
-      <c r="T13" s="39"/>
-      <c r="U13" s="39"/>
-      <c r="V13" s="39"/>
-      <c r="W13" s="39"/>
-      <c r="X13" s="39" t="s">
-        <v>224</v>
-      </c>
-      <c r="Y13" s="39"/>
-      <c r="Z13" s="39"/>
-      <c r="AA13" s="39"/>
-      <c r="AB13" s="39"/>
-      <c r="AC13" s="39"/>
-      <c r="AD13" s="39"/>
-      <c r="AE13" s="39"/>
-      <c r="AF13" s="39"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="29"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="29"/>
+      <c r="T13" s="29"/>
+      <c r="U13" s="29"/>
+      <c r="V13" s="29"/>
+      <c r="W13" s="29"/>
+      <c r="X13" s="29" t="s">
+        <v>224</v>
+      </c>
+      <c r="Y13" s="29"/>
+      <c r="Z13" s="29"/>
+      <c r="AA13" s="29"/>
+      <c r="AB13" s="29"/>
+      <c r="AC13" s="29"/>
+      <c r="AD13" s="29"/>
+      <c r="AE13" s="29"/>
+      <c r="AF13" s="29"/>
     </row>
-    <row r="14" spans="1:33" ht="24">
+    <row r="14" spans="1:33" s="23" customFormat="1" ht="21.75" customHeight="1">
       <c r="A14" s="29" t="s">
         <v>278</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="29" t="s">
         <v>277</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="39"/>
-      <c r="L14" s="39"/>
-      <c r="M14" s="39"/>
-      <c r="N14" s="40"/>
-      <c r="O14" s="39"/>
-      <c r="P14" s="39"/>
-      <c r="Q14" s="39"/>
-      <c r="R14" s="39"/>
-      <c r="S14" s="39"/>
-      <c r="T14" s="39"/>
-      <c r="U14" s="39"/>
-      <c r="V14" s="39"/>
-      <c r="W14" s="39"/>
-      <c r="X14" s="39" t="s">
-        <v>224</v>
-      </c>
-      <c r="Y14" s="39"/>
-      <c r="Z14" s="39"/>
-      <c r="AA14" s="39"/>
-      <c r="AB14" s="39"/>
-      <c r="AC14" s="39"/>
-      <c r="AD14" s="39"/>
-      <c r="AE14" s="39"/>
-      <c r="AF14" s="39"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="29"/>
+      <c r="N14" s="29"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="29"/>
+      <c r="R14" s="29"/>
+      <c r="S14" s="29"/>
+      <c r="T14" s="29"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="29"/>
+      <c r="W14" s="29"/>
+      <c r="X14" s="29" t="s">
+        <v>224</v>
+      </c>
+      <c r="Y14" s="29"/>
+      <c r="Z14" s="29"/>
+      <c r="AA14" s="29"/>
+      <c r="AB14" s="29"/>
+      <c r="AC14" s="29"/>
+      <c r="AD14" s="29"/>
+      <c r="AE14" s="29"/>
+      <c r="AF14" s="29"/>
+    </row>
+    <row r="15" spans="1:33" s="23" customFormat="1" ht="25.5" customHeight="1">
+      <c r="A15" s="29" t="s">
+        <v>279</v>
+      </c>
+      <c r="B15" s="29" t="s">
+        <v>277</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="29"/>
+      <c r="R15" s="29"/>
+      <c r="S15" s="29"/>
+      <c r="T15" s="29"/>
+      <c r="U15" s="29"/>
+      <c r="V15" s="29"/>
+      <c r="W15" s="29"/>
+      <c r="X15" s="29" t="s">
+        <v>224</v>
+      </c>
+      <c r="Y15" s="29"/>
+      <c r="Z15" s="29"/>
+      <c r="AA15" s="29"/>
+      <c r="AB15" s="29"/>
+      <c r="AC15" s="29"/>
+      <c r="AD15" s="29"/>
+      <c r="AE15" s="29"/>
+      <c r="AF15" s="29"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AC2" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
@@ -2872,7 +2911,7 @@
     <mergeCell ref="A8:A9"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="P2:P3 M3 W2 V3 M2:N2 I2:K3 M12:N12 U12:X12 AB12:AC12 N4:N11 R12:S12 W4:W11 J4:L201 Q4:Q201 N13:N201 W13:W201" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="P2:P3 M3 W2 V3 M2:N2 I2:K3 M12:N12 U12:X12 AB12:AC12 N4:N11 R12:S12 W4:W11 W13:W201 N13:N201 Q4:Q201 J4:L201" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Yes,No,Partial,N/A,Not recorded"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/data/report.xlsx
+++ b/data/report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bank Muscat\AD Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="417" documentId="13_ncr:1_{4A272BF1-49BC-4E00-83C3-F2030B573C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0264B50-D87E-450A-8522-77D1B34FEEA7}"/>
+  <xr:revisionPtr revIDLastSave="418" documentId="13_ncr:1_{4A272BF1-49BC-4E00-83C3-F2030B573C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFC28620-3C44-4670-ABB3-89CF2DFA21E8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="278">
   <si>
     <t>Client / entity</t>
   </si>
@@ -915,12 +915,6 @@
   </si>
   <si>
     <t>Anomaly Deyection in Bank</t>
-  </si>
-  <si>
-    <t>Project Test 456</t>
-  </si>
-  <si>
-    <t>Project Test 789100</t>
   </si>
 </sst>
 </file>
@@ -1643,7 +1637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AG15"/>
+  <dimension ref="A1:AG13"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="23" customWidth="1"/>
@@ -2819,90 +2813,6 @@
       <c r="AE13" s="29"/>
       <c r="AF13" s="29"/>
     </row>
-    <row r="14" spans="1:33" s="23" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A14" s="29" t="s">
-        <v>278</v>
-      </c>
-      <c r="B14" s="29" t="s">
-        <v>277</v>
-      </c>
-      <c r="C14" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="29"/>
-      <c r="L14" s="29"/>
-      <c r="M14" s="29"/>
-      <c r="N14" s="29"/>
-      <c r="O14" s="29"/>
-      <c r="P14" s="29"/>
-      <c r="Q14" s="29"/>
-      <c r="R14" s="29"/>
-      <c r="S14" s="29"/>
-      <c r="T14" s="29"/>
-      <c r="U14" s="29"/>
-      <c r="V14" s="29"/>
-      <c r="W14" s="29"/>
-      <c r="X14" s="29" t="s">
-        <v>224</v>
-      </c>
-      <c r="Y14" s="29"/>
-      <c r="Z14" s="29"/>
-      <c r="AA14" s="29"/>
-      <c r="AB14" s="29"/>
-      <c r="AC14" s="29"/>
-      <c r="AD14" s="29"/>
-      <c r="AE14" s="29"/>
-      <c r="AF14" s="29"/>
-    </row>
-    <row r="15" spans="1:33" s="23" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A15" s="29" t="s">
-        <v>279</v>
-      </c>
-      <c r="B15" s="29" t="s">
-        <v>277</v>
-      </c>
-      <c r="C15" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="29"/>
-      <c r="K15" s="29"/>
-      <c r="L15" s="29"/>
-      <c r="M15" s="29"/>
-      <c r="N15" s="29"/>
-      <c r="O15" s="29"/>
-      <c r="P15" s="29"/>
-      <c r="Q15" s="29"/>
-      <c r="R15" s="29"/>
-      <c r="S15" s="29"/>
-      <c r="T15" s="29"/>
-      <c r="U15" s="29"/>
-      <c r="V15" s="29"/>
-      <c r="W15" s="29"/>
-      <c r="X15" s="29" t="s">
-        <v>224</v>
-      </c>
-      <c r="Y15" s="29"/>
-      <c r="Z15" s="29"/>
-      <c r="AA15" s="29"/>
-      <c r="AB15" s="29"/>
-      <c r="AC15" s="29"/>
-      <c r="AD15" s="29"/>
-      <c r="AE15" s="29"/>
-      <c r="AF15" s="29"/>
-    </row>
   </sheetData>
   <autoFilter ref="A1:AC2" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="3">
@@ -2911,7 +2821,7 @@
     <mergeCell ref="A8:A9"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="P2:P3 M3 W2 V3 M2:N2 I2:K3 M12:N12 U12:X12 AB12:AC12 N4:N11 R12:S12 W4:W11 W13:W201 N13:N201 Q4:Q201 J4:L201" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="P2:P3 M3 W2 V3 M2:N2 I2:K3 M12:N12 U12:X12 AB12:AC12 N4:N11 R12:S12 W4:W11 J4:L199 Q4:Q199 N13:N199 W13:W199" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Yes,No,Partial,N/A,Not recorded"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/data/report.xlsx
+++ b/data/report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bank Muscat\AD Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="418" documentId="13_ncr:1_{4A272BF1-49BC-4E00-83C3-F2030B573C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFC28620-3C44-4670-ABB3-89CF2DFA21E8}"/>
+  <xr:revisionPtr revIDLastSave="425" documentId="13_ncr:1_{4A272BF1-49BC-4E00-83C3-F2030B573C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04017921-2148-4B03-827B-CA336D80F345}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1173,7 +1173,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1312,6 +1312,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1445,7 +1448,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="39538275" y="11763375"/>
+          <a:off x="40176450" y="11763375"/>
           <a:ext cx="2981325" cy="1257300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1788,7 +1791,7 @@
       <c r="D2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="47" t="s">
         <v>36</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -2599,7 +2602,7 @@
       <c r="D11" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="24" t="s">
         <v>238</v>
       </c>
       <c r="F11" s="15" t="s">

--- a/data/report.xlsx
+++ b/data/report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bank Muscat\AD Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="425" documentId="13_ncr:1_{4A272BF1-49BC-4E00-83C3-F2030B573C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04017921-2148-4B03-827B-CA336D80F345}"/>
+  <xr:revisionPtr revIDLastSave="436" documentId="13_ncr:1_{4A272BF1-49BC-4E00-83C3-F2030B573C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2441048D-3FC5-4014-ACBF-0B46C8DB73E2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="279">
   <si>
     <t>Client / entity</t>
   </si>
@@ -911,10 +911,13 @@
     <t>LLMApp /getResponse JSON consumed by the AD SOE portal; DataApp Postgres tables per measure + analysis cache; IOApp markdown of uploaded documents in MinIO; MinIOApp document list/get/delete</t>
   </si>
   <si>
-    <t>Project Test 123</t>
+    <t>dfgdfgdf</t>
   </si>
   <si>
     <t>Anomaly Deyection in Bank</t>
+  </si>
+  <si>
+    <t>dfdfdd</t>
   </si>
 </sst>
 </file>
@@ -970,7 +973,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1052,6 +1055,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4FCE7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1173,7 +1188,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1211,9 +1226,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1244,12 +1256,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1277,9 +1283,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1313,8 +1316,26 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1391,6 +1412,7 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
     <mruColors>
+      <color rgb="FFD4FCE7"/>
       <color rgb="FFFFFFCC"/>
       <color rgb="FF00A87C"/>
       <color rgb="FFC40087"/>
@@ -1640,44 +1662,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AG13"/>
+  <dimension ref="A1:AG14"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" style="23" customWidth="1"/>
-    <col min="2" max="2" width="26.140625" style="22" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" style="22" customWidth="1"/>
-    <col min="4" max="4" width="24.140625" style="22" customWidth="1"/>
-    <col min="5" max="5" width="19" style="22" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" style="22" customWidth="1"/>
-    <col min="7" max="7" width="23.5703125" style="22" customWidth="1"/>
-    <col min="8" max="8" width="15" style="22" customWidth="1"/>
-    <col min="9" max="9" width="18" style="22" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" style="22" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" style="21" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="21" customWidth="1"/>
+    <col min="4" max="4" width="24.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="32.7109375" style="21" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" style="21" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" style="21" customWidth="1"/>
+    <col min="8" max="8" width="15" style="21" customWidth="1"/>
+    <col min="9" max="9" width="18" style="21" customWidth="1"/>
     <col min="10" max="10" width="19.42578125" style="12" customWidth="1"/>
-    <col min="11" max="11" width="25.5703125" style="22" customWidth="1"/>
-    <col min="12" max="12" width="21.5703125" style="22" customWidth="1"/>
-    <col min="13" max="13" width="29.85546875" style="22" customWidth="1"/>
+    <col min="11" max="11" width="25.5703125" style="21" customWidth="1"/>
+    <col min="12" max="12" width="21.5703125" style="21" customWidth="1"/>
+    <col min="13" max="13" width="29.85546875" style="21" customWidth="1"/>
     <col min="14" max="14" width="13.85546875" style="12" customWidth="1"/>
-    <col min="15" max="15" width="20.28515625" style="22" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.7109375" style="22" customWidth="1"/>
-    <col min="17" max="17" width="22.140625" style="22" customWidth="1"/>
-    <col min="18" max="18" width="20.140625" style="22" customWidth="1"/>
-    <col min="19" max="19" width="26" style="22" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19.28515625" style="22" customWidth="1"/>
-    <col min="21" max="21" width="20.5703125" style="22" customWidth="1"/>
-    <col min="22" max="22" width="18.28515625" style="22" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.42578125" style="22" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="19.7109375" style="22" customWidth="1"/>
-    <col min="25" max="25" width="28.140625" style="22" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.42578125" style="22" customWidth="1"/>
-    <col min="27" max="27" width="22.28515625" style="22" customWidth="1"/>
-    <col min="28" max="28" width="20.5703125" style="22" customWidth="1"/>
-    <col min="29" max="29" width="21.85546875" style="22" customWidth="1"/>
-    <col min="30" max="30" width="50.140625" style="22" customWidth="1"/>
-    <col min="31" max="31" width="32.85546875" style="22" customWidth="1"/>
-    <col min="32" max="32" width="19.85546875" style="22" customWidth="1"/>
-    <col min="33" max="33" width="16.140625" style="22" hidden="1" customWidth="1"/>
-    <col min="34" max="34" width="13.140625" style="22" customWidth="1"/>
-    <col min="35" max="16384" width="8.7109375" style="22"/>
+    <col min="15" max="15" width="20.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.7109375" style="21" customWidth="1"/>
+    <col min="17" max="17" width="22.140625" style="21" customWidth="1"/>
+    <col min="18" max="18" width="20.140625" style="21" customWidth="1"/>
+    <col min="19" max="19" width="26" style="21" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.28515625" style="21" customWidth="1"/>
+    <col min="21" max="21" width="20.5703125" style="21" customWidth="1"/>
+    <col min="22" max="22" width="18.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.42578125" style="21" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="19.7109375" style="21" customWidth="1"/>
+    <col min="25" max="25" width="28.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.42578125" style="21" customWidth="1"/>
+    <col min="27" max="27" width="22.28515625" style="21" customWidth="1"/>
+    <col min="28" max="28" width="20.5703125" style="21" customWidth="1"/>
+    <col min="29" max="29" width="21.85546875" style="21" customWidth="1"/>
+    <col min="30" max="30" width="50.140625" style="21" customWidth="1"/>
+    <col min="31" max="31" width="32.85546875" style="21" customWidth="1"/>
+    <col min="32" max="32" width="19.85546875" style="21" customWidth="1"/>
+    <col min="33" max="33" width="16.140625" style="21" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="13.140625" style="21" customWidth="1"/>
+    <col min="35" max="16384" width="8.7109375" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="12" customFormat="1" ht="45.75" customHeight="1">
@@ -1765,21 +1787,21 @@
       <c r="AB1" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="30" t="s">
+      <c r="AC1" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="26" t="s">
+      <c r="AD1" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="26" t="s">
+      <c r="AE1" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="26" t="s">
+      <c r="AF1" s="23" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:33" s="14" customFormat="1" ht="166.5">
-      <c r="A2" s="41" t="s">
+    <row r="2" spans="1:33" s="13" customFormat="1" ht="166.5">
+      <c r="A2" s="37" t="s">
         <v>32</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1791,7 +1813,7 @@
       <c r="D2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="47" t="s">
+      <c r="E2" s="44" t="s">
         <v>36</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -1861,17 +1883,17 @@
       <c r="AB2" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC2" s="31" t="s">
+      <c r="AC2" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="AD2" s="27"/>
-      <c r="AE2" s="27"/>
-      <c r="AF2" s="27" t="s">
+      <c r="AD2" s="24"/>
+      <c r="AE2" s="24"/>
+      <c r="AF2" s="24" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:33" s="14" customFormat="1" ht="130.5">
-      <c r="A3" s="42"/>
+    <row r="3" spans="1:33" s="13" customFormat="1" ht="130.5">
+      <c r="A3" s="38"/>
       <c r="B3" s="1" t="s">
         <v>61</v>
       </c>
@@ -1881,7 +1903,7 @@
       <c r="D3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="45" t="s">
         <v>63</v>
       </c>
       <c r="F3" s="2" t="s">
@@ -1951,20 +1973,20 @@
       <c r="AB3" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AC3" s="31" t="s">
+      <c r="AC3" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="AD3" s="27"/>
-      <c r="AE3" s="27"/>
-      <c r="AF3" s="27" t="s">
+      <c r="AD3" s="24"/>
+      <c r="AE3" s="24"/>
+      <c r="AF3" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="AG3" s="14" t="s">
+      <c r="AG3" s="13" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:33" s="17" customFormat="1" ht="63.6" customHeight="1">
-      <c r="A4" s="43"/>
+    <row r="4" spans="1:33" s="16" customFormat="1" ht="63.6" customHeight="1">
+      <c r="A4" s="39"/>
       <c r="B4" s="1" t="s">
         <v>72</v>
       </c>
@@ -1974,15 +1996,15 @@
       <c r="D4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="15"/>
+      <c r="E4" s="14"/>
       <c r="F4" s="2" t="s">
         <v>64</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15" t="s">
+      <c r="H4" s="14"/>
+      <c r="I4" s="14" t="s">
         <v>74</v>
       </c>
       <c r="J4" s="4" t="s">
@@ -1994,827 +2016,832 @@
       <c r="L4" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="M4" s="15" t="s">
+      <c r="M4" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="N4" s="16" t="s">
+      <c r="N4" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15" t="s">
+      <c r="O4" s="14"/>
+      <c r="P4" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="Q4" s="15" t="s">
+      <c r="Q4" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="R4" s="15" t="s">
+      <c r="R4" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="S4" s="15" t="s">
+      <c r="S4" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="T4" s="15" t="s">
+      <c r="T4" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="U4" s="15" t="s">
+      <c r="U4" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="V4" s="15" t="s">
+      <c r="V4" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="W4" s="15" t="s">
+      <c r="W4" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="X4" s="15" t="s">
+      <c r="X4" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="Y4" s="15" t="s">
+      <c r="Y4" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="Z4" s="15"/>
-      <c r="AA4" s="15"/>
-      <c r="AB4" s="15" t="s">
+      <c r="Z4" s="14"/>
+      <c r="AA4" s="14"/>
+      <c r="AB4" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="AC4" s="32" t="s">
+      <c r="AC4" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="AD4" s="28"/>
-      <c r="AE4" s="28"/>
-      <c r="AF4" s="27" t="s">
+      <c r="AD4" s="25"/>
+      <c r="AE4" s="25"/>
+      <c r="AF4" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="AG4" s="14" t="s">
+      <c r="AG4" s="13" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:33" s="17" customFormat="1" ht="84">
-      <c r="A5" s="44" t="s">
+    <row r="5" spans="1:33" s="16" customFormat="1" ht="84">
+      <c r="A5" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="J5" s="18" t="s">
+      <c r="J5" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="K5" s="19" t="s">
+      <c r="K5" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="M5" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="N5" s="16" t="s">
+      <c r="N5" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="O5" s="15" t="s">
+      <c r="O5" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="P5" s="15" t="s">
+      <c r="P5" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="Q5" s="15" t="s">
+      <c r="Q5" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="R5" s="15" t="s">
+      <c r="R5" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="S5" s="15" t="s">
+      <c r="S5" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="T5" s="15" t="s">
+      <c r="T5" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="U5" s="15" t="s">
+      <c r="U5" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="V5" s="15" t="s">
+      <c r="V5" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="W5" s="15" t="s">
+      <c r="W5" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="X5" s="15" t="s">
+      <c r="X5" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="Y5" s="15" t="s">
+      <c r="Y5" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="Z5" s="15" t="s">
+      <c r="Z5" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="AA5" s="15" t="s">
+      <c r="AA5" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="AB5" s="15" t="s">
+      <c r="AB5" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="AC5" s="32" t="s">
+      <c r="AC5" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="AD5" s="28"/>
-      <c r="AE5" s="28"/>
-      <c r="AF5" s="28"/>
+      <c r="AD5" s="25"/>
+      <c r="AE5" s="25"/>
+      <c r="AF5" s="25"/>
     </row>
-    <row r="6" spans="1:33" s="17" customFormat="1" ht="84">
-      <c r="A6" s="45"/>
-      <c r="B6" s="15" t="s">
+    <row r="6" spans="1:33" s="16" customFormat="1" ht="84">
+      <c r="A6" s="41"/>
+      <c r="B6" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="J6" s="18" t="s">
+      <c r="J6" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="K6" s="19" t="s">
+      <c r="K6" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="L6" s="15" t="s">
+      <c r="L6" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="M6" s="15" t="s">
+      <c r="M6" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="N6" s="16" t="s">
+      <c r="N6" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="O6" s="15" t="s">
+      <c r="O6" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="P6" s="15" t="s">
+      <c r="P6" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="Q6" s="15" t="s">
+      <c r="Q6" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="R6" s="15" t="s">
+      <c r="R6" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="S6" s="15" t="s">
+      <c r="S6" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="T6" s="15" t="s">
+      <c r="T6" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="U6" s="15" t="s">
+      <c r="U6" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="V6" s="15" t="s">
+      <c r="V6" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="W6" s="15" t="s">
+      <c r="W6" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="X6" s="15" t="s">
+      <c r="X6" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="Y6" s="15" t="s">
+      <c r="Y6" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="Z6" s="15" t="s">
+      <c r="Z6" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="AA6" s="15" t="s">
+      <c r="AA6" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="AB6" s="15" t="s">
+      <c r="AB6" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="AC6" s="32" t="s">
+      <c r="AC6" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="AD6" s="28"/>
-      <c r="AE6" s="28"/>
-      <c r="AF6" s="28"/>
+      <c r="AD6" s="25"/>
+      <c r="AE6" s="25"/>
+      <c r="AF6" s="25"/>
     </row>
-    <row r="7" spans="1:33" s="17" customFormat="1" ht="72">
-      <c r="A7" s="46"/>
-      <c r="B7" s="15" t="s">
+    <row r="7" spans="1:33" s="16" customFormat="1" ht="72">
+      <c r="A7" s="42"/>
+      <c r="B7" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="43" t="s">
         <v>144</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="I7" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="J7" s="18" t="s">
+      <c r="J7" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="K7" s="19" t="s">
+      <c r="K7" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="L7" s="15" t="s">
+      <c r="L7" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="M7" s="15" t="s">
+      <c r="M7" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="N7" s="16" t="s">
+      <c r="N7" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="O7" s="15" t="s">
+      <c r="O7" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="P7" s="15" t="s">
+      <c r="P7" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="Q7" s="15" t="s">
+      <c r="Q7" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="R7" s="15" t="s">
+      <c r="R7" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="S7" s="15" t="s">
+      <c r="S7" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="T7" s="15" t="s">
+      <c r="T7" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="U7" s="15" t="s">
+      <c r="U7" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="V7" s="15" t="s">
+      <c r="V7" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="W7" s="15" t="s">
+      <c r="W7" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="X7" s="15" t="s">
+      <c r="X7" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="Y7" s="15" t="s">
+      <c r="Y7" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="Z7" s="15" t="s">
+      <c r="Z7" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="AA7" s="15" t="s">
+      <c r="AA7" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="AB7" s="15" t="s">
+      <c r="AB7" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="AC7" s="32" t="s">
+      <c r="AC7" s="29" t="s">
         <v>166</v>
       </c>
-      <c r="AD7" s="28"/>
-      <c r="AE7" s="28"/>
-      <c r="AF7" s="28"/>
+      <c r="AD7" s="25"/>
+      <c r="AE7" s="25"/>
+      <c r="AF7" s="25"/>
     </row>
     <row r="8" spans="1:33" ht="130.5" customHeight="1">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="40" t="s">
         <v>167</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="46" t="s">
         <v>170</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="J8" s="18" t="s">
+      <c r="J8" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="K8" s="19" t="s">
+      <c r="K8" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="L8" s="15" t="s">
+      <c r="L8" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="M8" s="15" t="s">
+      <c r="M8" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="N8" s="16" t="s">
+      <c r="N8" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="O8" s="15" t="s">
+      <c r="O8" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="P8" s="15" t="s">
+      <c r="P8" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="Q8" s="15" t="s">
+      <c r="Q8" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="R8" s="15" t="s">
+      <c r="R8" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="S8" s="15" t="s">
+      <c r="S8" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="T8" s="15" t="s">
+      <c r="T8" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="U8" s="15" t="s">
+      <c r="U8" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="V8" s="15" t="s">
+      <c r="V8" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="W8" s="15" t="s">
+      <c r="W8" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="X8" s="15" t="s">
+      <c r="X8" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="Y8" s="15" t="s">
+      <c r="Y8" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="Z8" s="15" t="s">
+      <c r="Z8" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="AA8" s="15" t="s">
+      <c r="AA8" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="AB8" s="15" t="s">
+      <c r="AB8" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="AC8" s="32" t="s">
+      <c r="AC8" s="29" t="s">
         <v>194</v>
       </c>
-      <c r="AD8" s="28"/>
-      <c r="AE8" s="28"/>
-      <c r="AF8" s="27" t="s">
+      <c r="AD8" s="25"/>
+      <c r="AE8" s="25"/>
+      <c r="AF8" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="AG8" s="17"/>
+      <c r="AG8" s="16"/>
     </row>
-    <row r="9" spans="1:33" s="23" customFormat="1" ht="122.25" customHeight="1">
-      <c r="A9" s="46"/>
-      <c r="B9" s="15" t="s">
+    <row r="9" spans="1:33" s="22" customFormat="1" ht="122.25" customHeight="1">
+      <c r="A9" s="42"/>
+      <c r="B9" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="47" t="s">
         <v>198</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="G9" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="H9" s="16" t="s">
+      <c r="H9" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="I9" s="16" t="s">
+      <c r="I9" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="J9" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="K9" s="16" t="s">
+      <c r="K9" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16" t="s">
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="O9" s="16" t="s">
+      <c r="O9" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="P9" s="16" t="s">
+      <c r="P9" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="Q9" s="16" t="s">
+      <c r="Q9" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="R9" s="16" t="s">
+      <c r="R9" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="S9" s="16" t="s">
+      <c r="S9" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="T9" s="16" t="s">
+      <c r="T9" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="U9" s="16"/>
-      <c r="V9" s="16"/>
-      <c r="W9" s="16"/>
-      <c r="X9" s="16" t="s">
+      <c r="U9" s="15"/>
+      <c r="V9" s="15"/>
+      <c r="W9" s="15"/>
+      <c r="X9" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="Y9" s="16"/>
-      <c r="Z9" s="16" t="s">
+      <c r="Y9" s="15"/>
+      <c r="Z9" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="AA9" s="16" t="s">
+      <c r="AA9" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="AB9" s="16"/>
-      <c r="AC9" s="32" t="s">
+      <c r="AB9" s="15"/>
+      <c r="AC9" s="29" t="s">
         <v>215</v>
       </c>
-      <c r="AD9" s="29"/>
-      <c r="AE9" s="29"/>
-      <c r="AF9" s="27" t="s">
+      <c r="AD9" s="26"/>
+      <c r="AE9" s="26"/>
+      <c r="AF9" s="24" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="10" spans="1:33" s="17" customFormat="1" ht="171" customHeight="1">
-      <c r="A10" s="21" t="s">
+    <row r="10" spans="1:33" s="16" customFormat="1" ht="171" customHeight="1">
+      <c r="A10" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="48" t="s">
         <v>220</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="H10" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="I10" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="J10" s="18" t="s">
+      <c r="J10" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="K10" s="15" t="s">
+      <c r="K10" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="L10" s="15" t="s">
+      <c r="L10" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="M10" s="15" t="s">
+      <c r="M10" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="N10" s="16" t="s">
+      <c r="N10" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="O10" s="15" t="s">
+      <c r="O10" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="P10" s="15" t="s">
+      <c r="P10" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="Q10" s="15" t="s">
+      <c r="Q10" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="R10" s="15" t="s">
+      <c r="R10" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="S10" s="15" t="s">
+      <c r="S10" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="T10" s="15" t="s">
+      <c r="T10" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="U10" s="15" t="s">
+      <c r="U10" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="V10" s="15" t="s">
+      <c r="V10" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="W10" s="15" t="s">
+      <c r="W10" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="X10" s="15" t="s">
+      <c r="X10" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="Y10" s="15" t="s">
+      <c r="Y10" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="Z10" s="15" t="s">
+      <c r="Z10" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="AA10" s="15" t="s">
+      <c r="AA10" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="AB10" s="15" t="s">
+      <c r="AB10" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="AC10" s="32" t="s">
+      <c r="AC10" s="29" t="s">
         <v>224</v>
       </c>
-      <c r="AD10" s="28"/>
-      <c r="AE10" s="28" t="s">
+      <c r="AD10" s="25"/>
+      <c r="AE10" s="25" t="s">
         <v>232</v>
       </c>
-      <c r="AF10" s="28" t="s">
+      <c r="AF10" s="25" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:33" ht="166.5">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="43" t="s">
         <v>238</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="14" t="s">
         <v>240</v>
       </c>
-      <c r="H11" s="15" t="s">
+      <c r="H11" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="I11" s="15" t="s">
+      <c r="I11" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="J11" s="18" t="s">
+      <c r="J11" s="17" t="s">
         <v>243</v>
       </c>
-      <c r="K11" s="19" t="s">
+      <c r="K11" s="18" t="s">
         <v>244</v>
       </c>
-      <c r="L11" s="15" t="s">
+      <c r="L11" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="M11" s="15" t="s">
+      <c r="M11" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="N11" s="16" t="s">
+      <c r="N11" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="O11" s="15" t="s">
+      <c r="O11" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="P11" s="15" t="s">
+      <c r="P11" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="Q11" s="15" t="s">
+      <c r="Q11" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="R11" s="15">
+      <c r="R11" s="14">
         <v>1</v>
       </c>
-      <c r="S11" s="15" t="s">
+      <c r="S11" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="T11" s="15" t="s">
+      <c r="T11" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="U11" s="15" t="s">
+      <c r="U11" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="V11" s="15" t="s">
+      <c r="V11" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="W11" s="15" t="s">
+      <c r="W11" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="X11" s="15" t="s">
+      <c r="X11" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="Y11" s="15" t="s">
+      <c r="Y11" s="14" t="s">
         <v>257</v>
       </c>
-      <c r="Z11" s="15" t="s">
+      <c r="Z11" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="AA11" s="15" t="s">
+      <c r="AA11" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="AB11" s="15" t="s">
+      <c r="AB11" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="AC11" s="32"/>
-      <c r="AD11" s="28"/>
-      <c r="AE11" s="28"/>
-      <c r="AF11" s="28"/>
-      <c r="AG11" s="17"/>
+      <c r="AC11" s="29"/>
+      <c r="AD11" s="25"/>
+      <c r="AE11" s="25"/>
+      <c r="AF11" s="25"/>
+      <c r="AG11" s="16"/>
     </row>
-    <row r="12" spans="1:33" s="17" customFormat="1" ht="195" customHeight="1">
-      <c r="A12" s="33" t="s">
+    <row r="12" spans="1:33" s="16" customFormat="1" ht="195" customHeight="1">
+      <c r="A12" s="30" t="s">
         <v>261</v>
       </c>
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="31" t="s">
         <v>262</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" s="31" t="s">
         <v>263</v>
       </c>
-      <c r="D12" s="34" t="s">
+      <c r="D12" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="49" t="s">
         <v>265</v>
       </c>
-      <c r="F12" s="34" t="s">
+      <c r="F12" s="31" t="s">
         <v>266</v>
       </c>
-      <c r="G12" s="34" t="s">
+      <c r="G12" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="H12" s="34" t="s">
+      <c r="H12" s="31" t="s">
         <v>268</v>
       </c>
-      <c r="I12" s="34" t="s">
+      <c r="I12" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="J12" s="36" t="s">
+      <c r="J12" s="32" t="s">
         <v>224</v>
       </c>
-      <c r="K12" s="37" t="s">
+      <c r="K12" s="33" t="s">
         <v>224</v>
       </c>
-      <c r="L12" s="37" t="s">
+      <c r="L12" s="33" t="s">
         <v>224</v>
       </c>
-      <c r="M12" s="37" t="s">
+      <c r="M12" s="33" t="s">
         <v>224</v>
       </c>
-      <c r="N12" s="37" t="s">
+      <c r="N12" s="33" t="s">
         <v>269</v>
       </c>
-      <c r="O12" s="37" t="s">
+      <c r="O12" s="33" t="s">
         <v>270</v>
       </c>
-      <c r="P12" s="34" t="s">
+      <c r="P12" s="31" t="s">
         <v>271</v>
       </c>
-      <c r="Q12" s="37" t="s">
+      <c r="Q12" s="33" t="s">
         <v>224</v>
       </c>
-      <c r="R12" s="37" t="s">
+      <c r="R12" s="33" t="s">
         <v>224</v>
       </c>
-      <c r="S12" s="37" t="s">
+      <c r="S12" s="33" t="s">
         <v>224</v>
       </c>
-      <c r="T12" s="34" t="s">
+      <c r="T12" s="31" t="s">
         <v>272</v>
       </c>
-      <c r="U12" s="37" t="s">
+      <c r="U12" s="33" t="s">
         <v>224</v>
       </c>
-      <c r="V12" s="37" t="s">
+      <c r="V12" s="33" t="s">
         <v>224</v>
       </c>
-      <c r="W12" s="37" t="s">
+      <c r="W12" s="33" t="s">
         <v>224</v>
       </c>
-      <c r="X12" s="37" t="s">
+      <c r="X12" s="33" t="s">
         <v>224</v>
       </c>
-      <c r="Y12" s="34" t="s">
+      <c r="Y12" s="31" t="s">
         <v>273</v>
       </c>
-      <c r="Z12" s="34" t="s">
+      <c r="Z12" s="31" t="s">
         <v>274</v>
       </c>
-      <c r="AA12" s="34" t="s">
+      <c r="AA12" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="AB12" s="37" t="s">
+      <c r="AB12" s="33" t="s">
         <v>224</v>
       </c>
-      <c r="AC12" s="38" t="s">
+      <c r="AC12" s="34" t="s">
         <v>224</v>
       </c>
-      <c r="AD12" s="39"/>
-      <c r="AE12" s="39"/>
-      <c r="AF12" s="40" t="s">
+      <c r="AD12" s="35"/>
+      <c r="AE12" s="35"/>
+      <c r="AF12" s="36" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="13" spans="1:33" s="23" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A13" s="29" t="s">
+    <row r="13" spans="1:33" s="22" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A13" s="26" t="s">
         <v>276</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="26" t="s">
         <v>277</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29"/>
-      <c r="O13" s="29"/>
-      <c r="P13" s="29"/>
-      <c r="Q13" s="29"/>
-      <c r="R13" s="29"/>
-      <c r="S13" s="29"/>
-      <c r="T13" s="29"/>
-      <c r="U13" s="29"/>
-      <c r="V13" s="29"/>
-      <c r="W13" s="29"/>
-      <c r="X13" s="29" t="s">
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="26"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="26"/>
+      <c r="Q13" s="26"/>
+      <c r="R13" s="26"/>
+      <c r="S13" s="26"/>
+      <c r="T13" s="26"/>
+      <c r="U13" s="26"/>
+      <c r="V13" s="26"/>
+      <c r="W13" s="26"/>
+      <c r="X13" s="26" t="s">
         <v>224</v>
       </c>
-      <c r="Y13" s="29"/>
-      <c r="Z13" s="29"/>
-      <c r="AA13" s="29"/>
-      <c r="AB13" s="29"/>
-      <c r="AC13" s="29"/>
-      <c r="AD13" s="29"/>
-      <c r="AE13" s="29"/>
-      <c r="AF13" s="29"/>
+      <c r="Y13" s="26"/>
+      <c r="Z13" s="26"/>
+      <c r="AA13" s="26"/>
+      <c r="AB13" s="26"/>
+      <c r="AC13" s="26"/>
+      <c r="AD13" s="26"/>
+      <c r="AE13" s="26"/>
+      <c r="AF13" s="26"/>
+    </row>
+    <row r="14" spans="1:33">
+      <c r="A14" s="22" t="s">
+        <v>278</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AC2" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
